--- a/PICHINCHA/Julio/PICHINCHA-Julio.xlsx
+++ b/PICHINCHA/Julio/PICHINCHA-Julio.xlsx
@@ -5,23 +5,21 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PICHINCHA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94850E70-2A66-4502-9CF9-B5C9025BC34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076F7C49-9F99-44AE-A77E-2EE9A735B82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
-    <sheet name="EDESUR" sheetId="6" r:id="rId3"/>
-    <sheet name="Hoja1" sheetId="5" r:id="rId4"/>
-    <sheet name="extraordinaria" sheetId="4" r:id="rId5"/>
+    <sheet name="Hoja1" sheetId="5" r:id="rId3"/>
+    <sheet name="extraordinaria" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$A$1:$O$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$12</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="80">
   <si>
     <t>UF</t>
   </si>
@@ -244,48 +242,9 @@
     <t>PRIMER VTO</t>
   </si>
   <si>
-    <t xml:space="preserve">Edesur </t>
-  </si>
-  <si>
-    <t>EDESUR FACTURA 1:</t>
-  </si>
-  <si>
-    <t>EDESUR FACTURA 2:</t>
-  </si>
-  <si>
-    <t>EDESUR FACTURA 3:</t>
-  </si>
-  <si>
-    <t>GASTOS COMUNES</t>
-  </si>
-  <si>
-    <t>GASTOS COMUNES (SIN INCLUIR CONSUMO DE UF 3)</t>
-  </si>
-  <si>
-    <t>LOS GASTOS COMUNES INCLUYEN: CONSUMO DE LA BOMBA, LUCES DE ESCALERAS, TERRAZAS, COCHERAS Y PUERTAS, CAMARAS E INTERNET</t>
-  </si>
-  <si>
-    <t>SALDO A ABONAR</t>
-  </si>
-  <si>
-    <t>ABONADO</t>
-  </si>
-  <si>
-    <t>SALDO ANTERIOR</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Total abonado de Edesur</t>
-  </si>
-  <si>
     <t>METROGAS</t>
   </si>
   <si>
-    <t>FLOW - INTERNET CAMARA - AJUSTE ABONO</t>
-  </si>
-  <si>
     <t>ARBA</t>
   </si>
   <si>
@@ -299,6 +258,15 @@
   </si>
   <si>
     <t>ARTICULOS DE LIMPIEZA</t>
+  </si>
+  <si>
+    <t>FLOW - INTERNET CAMARA</t>
+  </si>
+  <si>
+    <t>EDESUR:</t>
+  </si>
+  <si>
+    <t>EDESUR</t>
   </si>
 </sst>
 </file>
@@ -306,10 +274,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -420,7 +388,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,26 +443,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="62">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -1136,126 +1086,6 @@
       </top>
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1265,7 +1095,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1467,54 +1297,22 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1566,8 +1364,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1935,23 +1733,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1959,27 +1757,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1987,13 +1785,13 @@
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
       <c r="E7" s="24" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F7" s="111" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2001,29 +1799,29 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="138" t="s">
+      <c r="E11" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="138"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="123"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
         <v>67</v>
       </c>
       <c r="B12" s="108"/>
-      <c r="C12" s="169">
+      <c r="C12" s="122">
         <v>33631.699999999997</v>
       </c>
       <c r="D12" s="5"/>
@@ -2034,11 +1832,11 @@
         <v>-735887.07199646719</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="169">
+      <c r="C13" s="122">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -2050,14 +1848,14 @@
         <v>564150.37439999986</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
         <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="80">
+      <c r="C14" s="145">
         <v>33600</v>
       </c>
       <c r="D14" s="5"/>
@@ -2065,330 +1863,326 @@
         <v>20</v>
       </c>
       <c r="F14" s="59">
-        <f>-(C37)</f>
-        <v>-445480.30000000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <f>-(C38)</f>
+        <v>-394521.68000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="168">
-        <v>106529.17</v>
+        <v>77</v>
+      </c>
+      <c r="C15" s="121">
+        <v>55570.55</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="58" t="s">
+      <c r="E15" s="58"/>
+      <c r="F15" s="59"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="59">
-        <f>-EDESUR!E7</f>
-        <v>-196908.95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="130">
+      <c r="C16" s="120">
         <v>71233.279999999999</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="59">
-        <f>EDESUR!E24</f>
-        <v>205464.27000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E16" s="58"/>
+      <c r="F16" s="59"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="130">
-        <v>12287</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="C17" s="120"/>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
       <c r="F17" s="59"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" s="130"/>
+        <v>75</v>
+      </c>
+      <c r="C18" s="120">
+        <v>12287</v>
+      </c>
+      <c r="D18" s="5"/>
       <c r="E18" s="58"/>
       <c r="F18" s="59"/>
-      <c r="H18" s="108"/>
-    </row>
-    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="32"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="87">
-        <f>SUM(C12:C18)</f>
-        <v>349367.15</v>
-      </c>
-      <c r="E19" s="60" t="s">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="120"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="59"/>
+      <c r="H19" s="108"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="32"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="87">
+        <f>SUM(C12:C19)</f>
+        <v>298408.53000000003</v>
+      </c>
+      <c r="E20" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="121">
-        <f>SUM(F12:F18)</f>
-        <v>-608661.67759646731</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="34" t="s">
+      <c r="F20" s="119">
+        <f>SUM(F12:F19)</f>
+        <v>-566258.37759646738</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="113"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="20"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="130">
-        <f>65203*5%+65203</f>
-        <v>68463.149999999994</v>
-      </c>
+      <c r="C21" s="113"/>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="168">
-        <v>27650</v>
+        <v>66</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="121">
+        <f>65203*5%+65203</f>
+        <v>68463.149999999994</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="31"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="130"/>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="121">
+        <v>27650</v>
+      </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="31"/>
       <c r="B24" s="35"/>
-      <c r="C24" s="130"/>
+      <c r="C24" s="120"/>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="31" t="s">
-        <v>60</v>
-      </c>
+    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="31"/>
       <c r="B25" s="35"/>
-      <c r="C25" s="112">
-        <f>550928.1-373926.22</f>
-        <v>177001.88</v>
-      </c>
+      <c r="C25" s="120"/>
       <c r="D25" s="5"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="109">
-        <f>SUM(C20:C25)</f>
-        <v>273115.03000000003</v>
-      </c>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="35"/>
+      <c r="C26" s="112"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="32"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="109">
+        <f>SUM(C21:C26)</f>
+        <v>96113.15</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="49">
-        <f>+C26+C19</f>
-        <v>622482.18000000005</v>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="20"/>
-    </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="82"/>
-      <c r="C28" s="83"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="49">
+        <f>+C27+C20</f>
+        <v>394521.68000000005</v>
+      </c>
+      <c r="D28" s="5"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="22" t="s">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="69" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="44"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="54"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="52"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="53">
-        <v>0</v>
-      </c>
+      <c r="B29" s="82"/>
+      <c r="C29" s="83"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="20"/>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="44"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="54"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="61"/>
-      <c r="B32" s="62"/>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="52"/>
+      <c r="B32" s="51"/>
       <c r="C32" s="53">
         <v>0</v>
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="78"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="81"/>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="61"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="53">
+        <v>0</v>
+      </c>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="78"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="86"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="81"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="78"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="81">
-        <v>0</v>
-      </c>
+      <c r="B35" s="85"/>
+      <c r="C35" s="86"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="63" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="78"/>
+      <c r="B36" s="84"/>
+      <c r="C36" s="81">
+        <v>0</v>
+      </c>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="64"/>
-      <c r="C36" s="65">
-        <f>SUM(C31:C35)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="B37" s="64"/>
+      <c r="C37" s="65">
+        <f>SUM(C32:C36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="53">
-        <f>C27-C25</f>
-        <v>445480.30000000005</v>
-      </c>
-      <c r="F37" s="6"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+      <c r="C38" s="53">
+        <f>C28-C26</f>
+        <v>394521.68000000005</v>
+      </c>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="77">
-        <f>+C27</f>
-        <v>622482.18000000005</v>
-      </c>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="63" t="s">
+      <c r="C39" s="77">
+        <f>+C28</f>
+        <v>394521.68000000005</v>
+      </c>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B39" s="64"/>
-      <c r="C39" s="65">
-        <f>+C27+C36</f>
-        <v>622482.18000000005</v>
-      </c>
-      <c r="E39" s="16"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="139"/>
-      <c r="C46" s="139"/>
-      <c r="D46" s="139"/>
-      <c r="E46" s="139"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="139"/>
-      <c r="C47" s="139"/>
-      <c r="D47" s="139"/>
-      <c r="E47" s="139"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="139"/>
-      <c r="C48" s="139"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="139"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="19"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="20"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="18"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="65">
+        <f>+C28+C37</f>
+        <v>394521.68000000005</v>
+      </c>
+      <c r="E40" s="16"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="124"/>
+      <c r="C47" s="124"/>
+      <c r="D47" s="124"/>
+      <c r="E47" s="124"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="124"/>
+      <c r="C48" s="124"/>
+      <c r="D48" s="124"/>
+      <c r="E48" s="124"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="124"/>
+      <c r="C49" s="124"/>
+      <c r="D49" s="124"/>
+      <c r="E49" s="124"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="19"/>
       <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C61" s="20"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B46:E48"/>
+    <mergeCell ref="B47:E49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2406,33 +2200,37 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="105" t="s">
         <v>55</v>
       </c>
       <c r="B1" s="106"/>
       <c r="C1" s="106"/>
       <c r="D1" s="26"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="26"/>
+      <c r="E1" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="144">
+        <v>0</v>
+      </c>
       <c r="G1" s="25" t="s">
         <v>47</v>
       </c>
@@ -2445,7 +2243,7 @@
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="72" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de JULIO</v>
@@ -2465,7 +2263,7 @@
       <c r="L2" s="114"/>
       <c r="M2" s="76"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2506,7 +2304,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2540,7 +2338,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2586,7 +2384,7 @@
         <v>114593.04479999999</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2624,15 +2422,15 @@
         <v>0</v>
       </c>
       <c r="L6" s="15">
-        <f t="shared" ref="L6:L9" si="3">J6+K6+H6+G6</f>
+        <f>J6+K6+H6+G6</f>
         <v>110185.62</v>
       </c>
       <c r="M6" s="39">
-        <f t="shared" ref="M6:M9" si="4">L6*4%+L6</f>
+        <f t="shared" ref="M6:M9" si="3">L6*4%+L6</f>
         <v>114593.04479999999</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2647,7 +2445,7 @@
         <v>114593.04479999999</v>
       </c>
       <c r="F7" s="80">
-        <f t="shared" ref="F7:F8" si="5">E7</f>
+        <f t="shared" ref="F7:F8" si="4">E7</f>
         <v>114593.04479999999</v>
       </c>
       <c r="G7" s="67">
@@ -2670,15 +2468,15 @@
         <v>0</v>
       </c>
       <c r="L7" s="15">
+        <f>J7+K7+H7+G7</f>
+        <v>110185.62</v>
+      </c>
+      <c r="M7" s="39">
         <f t="shared" si="3"/>
-        <v>110185.62</v>
-      </c>
-      <c r="M7" s="39">
-        <f t="shared" si="4"/>
         <v>114593.04479999999</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2693,7 +2491,7 @@
         <v>114593.04479999999</v>
       </c>
       <c r="F8" s="80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>114593.04479999999</v>
       </c>
       <c r="G8" s="67">
@@ -2716,15 +2514,15 @@
         <v>0</v>
       </c>
       <c r="L8" s="15">
+        <f>J8+K8+H8+G8</f>
+        <v>110185.62</v>
+      </c>
+      <c r="M8" s="39">
         <f t="shared" si="3"/>
-        <v>110185.62</v>
-      </c>
-      <c r="M8" s="39">
-        <f t="shared" si="4"/>
         <v>114593.04479999999</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2762,126 +2560,126 @@
         <v>0</v>
       </c>
       <c r="L9" s="15">
+        <f>J9+K9+H9+G9</f>
+        <v>110185.62</v>
+      </c>
+      <c r="M9" s="39">
         <f t="shared" si="3"/>
-        <v>110185.62</v>
-      </c>
-      <c r="M9" s="39">
-        <f t="shared" si="4"/>
         <v>114593.04479999999</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="10"/>
       <c r="D10" s="45">
-        <f t="shared" ref="D10:M10" si="6">SUM(D5:D9)</f>
+        <f t="shared" ref="D10:M10" si="5">SUM(D5:D9)</f>
         <v>0</v>
       </c>
       <c r="E10" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>564150.37439999986</v>
       </c>
       <c r="F10" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>564150.37439999986</v>
       </c>
       <c r="G10" s="50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H10" s="50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I10" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J10" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>550928.1</v>
       </c>
       <c r="K10" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L10" s="118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>550928.1</v>
       </c>
       <c r="M10" s="118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>572965.22399999993</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="140"/>
-      <c r="B11" s="140"/>
-      <c r="C11" s="140"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="140"/>
-      <c r="M11" s="140"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="125"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="125"/>
+      <c r="K11" s="125"/>
+      <c r="L11" s="125"/>
+      <c r="M11" s="125"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="141"/>
-      <c r="D13" s="141"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="141"/>
-      <c r="H13" s="141"/>
-      <c r="I13" s="141"/>
-      <c r="J13" s="141"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="141"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="141"/>
-      <c r="D14" s="141"/>
-      <c r="E14" s="141"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="141"/>
-      <c r="H14" s="141"/>
-      <c r="I14" s="141"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="141"/>
-      <c r="L14" s="141"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="141"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="141"/>
-      <c r="H15" s="141"/>
-      <c r="I15" s="141"/>
-      <c r="J15" s="141"/>
-      <c r="K15" s="141"/>
-      <c r="L15" s="141"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="141"/>
-      <c r="D16" s="141"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="141"/>
-      <c r="H16" s="141"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="141"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="126"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="126"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="126"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="126"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="126"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="126"/>
+      <c r="H16" s="126"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2895,489 +2693,79 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797B6844-9F76-4FEE-994B-56DA20848B8C}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="5.33203125" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="14" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" style="21" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1"/>
-      <c r="B1"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2"/>
-      <c r="B2"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3"/>
-      <c r="B3"/>
-      <c r="K3" t="s">
-        <v>75</v>
-      </c>
-      <c r="M3" s="6">
-        <f>E6</f>
-        <v>59706.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4"/>
-      <c r="B4"/>
-      <c r="C4" s="124" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="124"/>
-      <c r="E4" s="135">
-        <v>79470.880000000005</v>
-      </c>
-      <c r="G4" t="s">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>76</v>
-      </c>
-      <c r="O4" s="120">
-        <f>M3-K8</f>
-        <v>-22787.35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
-      <c r="C5" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="136">
-        <v>57731.97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6" s="108" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="137">
-        <v>59706.1</v>
-      </c>
-      <c r="G6" s="124">
-        <v>1</v>
-      </c>
-      <c r="H6" s="124">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="124" t="s">
-        <v>62</v>
-      </c>
-      <c r="K6" s="120">
-        <f>E4/2</f>
-        <v>39735.440000000002</v>
-      </c>
-      <c r="L6" s="126">
-        <f>O$4/5</f>
-        <v>-4557.4699999999993</v>
-      </c>
-      <c r="N6" s="132">
-        <f>SUM(K6:M6)</f>
-        <v>35177.97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="123">
-        <f>SUM(E4:E6)</f>
-        <v>196908.95</v>
-      </c>
-      <c r="G7" s="125">
-        <v>2</v>
-      </c>
-      <c r="H7" s="125">
-        <v>2</v>
-      </c>
-      <c r="I7" s="125" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="125" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="120">
-        <f>E5/2</f>
-        <v>28865.985000000001</v>
-      </c>
-      <c r="L7" s="126">
-        <f>O$4/5</f>
-        <v>-4557.4699999999993</v>
-      </c>
-      <c r="N7" s="133">
-        <f t="shared" ref="N7:N10" si="0">SUM(K7:M7)</f>
-        <v>24308.514999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8"/>
-      <c r="B8"/>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K8" s="120">
-        <v>82493.45</v>
-      </c>
-      <c r="L8" s="126">
-        <f t="shared" ref="L8:L11" si="1">O$4/5</f>
-        <v>-4557.4699999999993</v>
-      </c>
-      <c r="N8" s="133">
-        <f t="shared" si="0"/>
-        <v>77935.98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9"/>
-      <c r="B9"/>
-      <c r="G9" s="125">
-        <v>4</v>
-      </c>
-      <c r="H9" s="125">
-        <v>4</v>
-      </c>
-      <c r="I9" s="125" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="125" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="120">
-        <f>E5/2</f>
-        <v>28865.985000000001</v>
-      </c>
-      <c r="L9" s="126">
-        <f t="shared" si="1"/>
-        <v>-4557.4699999999993</v>
-      </c>
-      <c r="N9" s="133">
-        <f t="shared" si="0"/>
-        <v>24308.514999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10"/>
-      <c r="B10"/>
-      <c r="G10" s="124">
-        <v>5</v>
-      </c>
-      <c r="H10" s="124">
-        <v>5</v>
-      </c>
-      <c r="I10" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="124" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" s="120">
-        <f>E4/2</f>
-        <v>39735.440000000002</v>
-      </c>
-      <c r="L10" s="126">
-        <f t="shared" si="1"/>
-        <v>-4557.4699999999993</v>
-      </c>
-      <c r="N10" s="134">
-        <f t="shared" si="0"/>
-        <v>35177.97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="L11" s="126">
-        <f t="shared" si="1"/>
-        <v>-4557.4699999999993</v>
-      </c>
-      <c r="N11" s="127"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12"/>
-      <c r="B12"/>
-      <c r="N12" s="127"/>
-    </row>
-    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13" s="129" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="129"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="129"/>
-      <c r="G13" s="129"/>
-      <c r="H13" s="129"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="129"/>
-      <c r="K13" s="129"/>
-      <c r="L13" s="129"/>
-      <c r="M13" s="129"/>
-      <c r="N13" s="127"/>
-    </row>
-    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="N14" s="128">
-        <f>SUM(N6:N13)</f>
-        <v>196908.94999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="119" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="119" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="119" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="145" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="146"/>
-      <c r="J17" s="147"/>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" s="120">
-        <v>27583.722000000002</v>
-      </c>
-      <c r="E18" s="131">
-        <f>C18</f>
-        <v>27583.722000000002</v>
-      </c>
-      <c r="F18" s="6">
-        <f>N6</f>
-        <v>35177.97</v>
-      </c>
-      <c r="H18" s="148">
-        <f>C18-E18+F18</f>
-        <v>35177.97</v>
-      </c>
-      <c r="I18" s="149"/>
-      <c r="J18" s="150"/>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="120">
-        <v>35812.577000000005</v>
-      </c>
-      <c r="E19" s="131">
-        <f t="shared" ref="E19:E22" si="2">C19</f>
-        <v>35812.577000000005</v>
-      </c>
-      <c r="F19" s="6">
-        <f>N7</f>
-        <v>24308.514999999999</v>
-      </c>
-      <c r="H19" s="148">
-        <f t="shared" ref="H19:H22" si="3">C19-E19+F19</f>
-        <v>24308.514999999999</v>
-      </c>
-      <c r="I19" s="149"/>
-      <c r="J19" s="150"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="120">
-        <v>78671.671999999991</v>
-      </c>
-      <c r="E20" s="131">
-        <f t="shared" si="2"/>
-        <v>78671.671999999991</v>
-      </c>
-      <c r="F20" s="6">
-        <f t="shared" ref="F20:F22" si="4">N8</f>
-        <v>77935.98</v>
-      </c>
-      <c r="H20" s="148">
-        <f>C20-E20+F20</f>
-        <v>77935.98</v>
-      </c>
-      <c r="I20" s="149"/>
-      <c r="J20" s="150"/>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="120">
-        <v>35812.577000000005</v>
-      </c>
-      <c r="E21" s="131">
-        <f t="shared" si="2"/>
-        <v>35812.577000000005</v>
-      </c>
-      <c r="F21" s="6">
-        <f>N9</f>
-        <v>24308.514999999999</v>
-      </c>
-      <c r="H21" s="148">
-        <f t="shared" si="3"/>
-        <v>24308.514999999999</v>
-      </c>
-      <c r="I21" s="149"/>
-      <c r="J21" s="150"/>
-    </row>
-    <row r="22" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C22" s="120">
-        <v>27583.722000000002</v>
-      </c>
-      <c r="E22" s="131">
-        <f t="shared" si="2"/>
-        <v>27583.722000000002</v>
-      </c>
-      <c r="F22" s="6">
-        <f t="shared" si="4"/>
-        <v>35177.97</v>
-      </c>
-      <c r="H22" s="142">
-        <f t="shared" si="3"/>
-        <v>35177.97</v>
-      </c>
-      <c r="I22" s="143"/>
-      <c r="J22" s="144"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E24" s="6">
-        <f>SUM(E18:E23)</f>
-        <v>205464.27000000002</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="93" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A59F83D-EB65-4E23-8775-704ADF1A523E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="156" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="158"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="159" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="135" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="162">
+      <c r="B2" s="136"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="138">
         <v>565</v>
       </c>
-      <c r="E2" s="163"/>
+      <c r="E2" s="139"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="164" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="164" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="140" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="164" t="s">
+      <c r="C3" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="166" t="s">
+      <c r="D3" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="151" t="s">
+      <c r="E3" s="127" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="151" t="s">
+      <c r="F3" s="127" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="151" t="s">
+      <c r="G3" s="127" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="165"/>
-      <c r="B4" s="165"/>
-      <c r="C4" s="165"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="141"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
         <v>1</v>
       </c>
@@ -3400,7 +2788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90">
         <v>2</v>
       </c>
@@ -3423,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="90">
         <v>3</v>
       </c>
@@ -3446,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="90">
         <v>4</v>
       </c>
@@ -3469,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="90">
         <v>5</v>
       </c>
@@ -3492,7 +2880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="95">
         <v>6</v>
       </c>
@@ -3515,7 +2903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="100" t="s">
         <v>8</v>
       </c>
@@ -3534,12 +2922,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="153"/>
-      <c r="B12" s="154"/>
-      <c r="C12" s="154"/>
-      <c r="D12" s="154"/>
-      <c r="E12" s="155"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="129"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="131"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>

--- a/PICHINCHA/Julio/PICHINCHA-Julio.xlsx
+++ b/PICHINCHA/Julio/PICHINCHA-Julio.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076F7C49-9F99-44AE-A77E-2EE9A735B82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F22CCDB-0CED-4160-8140-16E0C9EE0E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="5" r:id="rId3"/>
-    <sheet name="extraordinaria" sheetId="4" r:id="rId4"/>
+    <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$45</definedName>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
   <si>
     <t>UF</t>
   </si>
@@ -261,9 +260,6 @@
   </si>
   <si>
     <t>FLOW - INTERNET CAMARA</t>
-  </si>
-  <si>
-    <t>EDESUR:</t>
   </si>
   <si>
     <t>EDESUR</t>
@@ -279,7 +275,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,13 +376,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1095,7 +1084,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1299,8 +1288,7 @@
     <xf numFmtId="166" fontId="1" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1364,8 +1352,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1811,17 +1798,17 @@
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="123" t="s">
+      <c r="E11" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="123"/>
+      <c r="F11" s="122"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
         <v>67</v>
       </c>
       <c r="B12" s="108"/>
-      <c r="C12" s="122">
+      <c r="C12" s="143">
         <v>33631.699999999997</v>
       </c>
       <c r="D12" s="5"/>
@@ -1829,14 +1816,14 @@
         <v>42</v>
       </c>
       <c r="F12" s="57">
-        <v>-735887.07199646719</v>
+        <v>-537107.59759646724</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="122">
+      <c r="C13" s="143">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -1855,7 +1842,7 @@
       <c r="B14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="145">
+      <c r="C14" s="80">
         <v>33600</v>
       </c>
       <c r="D14" s="5"/>
@@ -1864,14 +1851,14 @@
       </c>
       <c r="F14" s="59">
         <f>-(C38)</f>
-        <v>-394521.68000000005</v>
+        <v>-488303.4</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="121">
+      <c r="C15" s="120">
         <v>55570.55</v>
       </c>
       <c r="D15" s="5"/>
@@ -1883,7 +1870,7 @@
         <v>71</v>
       </c>
       <c r="C16" s="120">
-        <v>71233.279999999999</v>
+        <v>99374.86</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="58"/>
@@ -1891,9 +1878,11 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="120"/>
+        <v>78</v>
+      </c>
+      <c r="C17" s="120">
+        <v>56349.64</v>
+      </c>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
       <c r="F17" s="59"/>
@@ -1903,7 +1892,7 @@
         <v>75</v>
       </c>
       <c r="C18" s="120">
-        <v>12287</v>
+        <v>14560</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="58"/>
@@ -1913,7 +1902,9 @@
       <c r="A19" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="120"/>
+      <c r="C19" s="120">
+        <v>7017.5</v>
+      </c>
       <c r="E19" s="58"/>
       <c r="F19" s="59"/>
       <c r="H19" s="108"/>
@@ -1923,14 +1914,14 @@
       <c r="B20" s="33"/>
       <c r="C20" s="87">
         <f>SUM(C12:C19)</f>
-        <v>298408.53000000003</v>
+        <v>392190.25</v>
       </c>
       <c r="E20" s="60" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="119">
         <f>SUM(F12:F19)</f>
-        <v>-566258.37759646738</v>
+        <v>-461260.62319646741</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1947,7 +1938,7 @@
         <v>66</v>
       </c>
       <c r="B22" s="35"/>
-      <c r="C22" s="121">
+      <c r="C22" s="120">
         <f>65203*5%+65203</f>
         <v>68463.149999999994</v>
       </c>
@@ -1959,7 +1950,7 @@
       <c r="A23" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="121">
+      <c r="C23" s="120">
         <v>27650</v>
       </c>
       <c r="D23" s="5"/>
@@ -2011,7 +2002,7 @@
       <c r="B28" s="48"/>
       <c r="C28" s="49">
         <f>+C27+C20</f>
-        <v>394521.68000000005</v>
+        <v>488303.4</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="19"/>
@@ -2089,7 +2080,7 @@
       </c>
       <c r="C38" s="53">
         <f>C28-C26</f>
-        <v>394521.68000000005</v>
+        <v>488303.4</v>
       </c>
       <c r="F38" s="6"/>
     </row>
@@ -2099,7 +2090,7 @@
       </c>
       <c r="C39" s="77">
         <f>+C28</f>
-        <v>394521.68000000005</v>
+        <v>488303.4</v>
       </c>
       <c r="F39" s="6"/>
     </row>
@@ -2110,7 +2101,7 @@
       <c r="B40" s="64"/>
       <c r="C40" s="65">
         <f>+C28+C37</f>
-        <v>394521.68000000005</v>
+        <v>488303.4</v>
       </c>
       <c r="E40" s="16"/>
     </row>
@@ -2122,22 +2113,22 @@
       <c r="E46" s="16"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="124"/>
-      <c r="C47" s="124"/>
-      <c r="D47" s="124"/>
-      <c r="E47" s="124"/>
+      <c r="B47" s="123"/>
+      <c r="C47" s="123"/>
+      <c r="D47" s="123"/>
+      <c r="E47" s="123"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="124"/>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
+      <c r="B48" s="123"/>
+      <c r="C48" s="123"/>
+      <c r="D48" s="123"/>
+      <c r="E48" s="123"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="124"/>
-      <c r="C49" s="124"/>
-      <c r="D49" s="124"/>
-      <c r="E49" s="124"/>
+      <c r="B49" s="123"/>
+      <c r="C49" s="123"/>
+      <c r="D49" s="123"/>
+      <c r="E49" s="123"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="19"/>
@@ -2225,12 +2216,8 @@
       <c r="B1" s="106"/>
       <c r="C1" s="106"/>
       <c r="D1" s="26"/>
-      <c r="E1" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="144">
-        <v>0</v>
-      </c>
+      <c r="E1" s="25"/>
+      <c r="F1" s="121"/>
       <c r="G1" s="25" t="s">
         <v>47</v>
       </c>
@@ -2238,7 +2225,7 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="71">
-        <v>550928.1</v>
+        <v>488303.4</v>
       </c>
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
@@ -2369,7 +2356,7 @@
       </c>
       <c r="J5" s="38">
         <f>K$1/5</f>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="K5" s="117">
         <f>K2*D5</f>
@@ -2377,11 +2364,11 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="M5" s="39">
         <f>L5*4%+L5</f>
-        <v>114593.04479999999</v>
+        <v>101567.10720000001</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -2415,7 +2402,7 @@
       </c>
       <c r="J6" s="38">
         <f t="shared" ref="J6:J9" si="2">K$1/5</f>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="K6" s="117">
         <f>K2*D6</f>
@@ -2423,11 +2410,11 @@
       </c>
       <c r="L6" s="15">
         <f>J6+K6+H6+G6</f>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="M6" s="39">
         <f t="shared" ref="M6:M9" si="3">L6*4%+L6</f>
-        <v>114593.04479999999</v>
+        <v>101567.10720000001</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2461,7 +2448,7 @@
       </c>
       <c r="J7" s="38">
         <f t="shared" si="2"/>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="K7" s="117">
         <f>K2*D7</f>
@@ -2469,11 +2456,11 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="M7" s="39">
         <f t="shared" si="3"/>
-        <v>114593.04479999999</v>
+        <v>101567.10720000001</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -2507,7 +2494,7 @@
       </c>
       <c r="J8" s="38">
         <f t="shared" si="2"/>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="K8" s="117">
         <f>K2*D8</f>
@@ -2515,11 +2502,11 @@
       </c>
       <c r="L8" s="15">
         <f>J8+K8+H8+G8</f>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="M8" s="39">
         <f t="shared" si="3"/>
-        <v>114593.04479999999</v>
+        <v>101567.10720000001</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2553,7 +2540,7 @@
       </c>
       <c r="J9" s="38">
         <f t="shared" si="2"/>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="K9" s="117">
         <f>K2*D9</f>
@@ -2561,11 +2548,11 @@
       </c>
       <c r="L9" s="15">
         <f>J9+K9+H9+G9</f>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" si="3"/>
-        <v>114593.04479999999</v>
+        <v>101567.10720000001</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2600,7 +2587,7 @@
       </c>
       <c r="J10" s="46">
         <f t="shared" si="5"/>
-        <v>550928.1</v>
+        <v>488303.4</v>
       </c>
       <c r="K10" s="46">
         <f t="shared" si="5"/>
@@ -2608,78 +2595,78 @@
       </c>
       <c r="L10" s="118">
         <f t="shared" si="5"/>
-        <v>550928.1</v>
+        <v>488303.4</v>
       </c>
       <c r="M10" s="118">
         <f t="shared" si="5"/>
-        <v>572965.22399999993</v>
+        <v>507835.53600000008</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="125"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="125"/>
-      <c r="K11" s="125"/>
-      <c r="L11" s="125"/>
-      <c r="M11" s="125"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="124"/>
+      <c r="K11" s="124"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="124"/>
     </row>
     <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="126"/>
-      <c r="L13" s="126"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="125"/>
+      <c r="K13" s="125"/>
+      <c r="L13" s="125"/>
     </row>
     <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="126"/>
-      <c r="D14" s="126"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="126"/>
-      <c r="J14" s="126"/>
-      <c r="K14" s="126"/>
-      <c r="L14" s="126"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="125"/>
+      <c r="K14" s="125"/>
+      <c r="L14" s="125"/>
     </row>
     <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126"/>
-      <c r="K15" s="126"/>
-      <c r="L15" s="126"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
     </row>
     <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="126"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="126"/>
-      <c r="I16" s="126"/>
-      <c r="J16" s="126"/>
-      <c r="K16" s="126"/>
-      <c r="L16" s="126"/>
+      <c r="C16" s="125"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="125"/>
+      <c r="J16" s="125"/>
+      <c r="K16" s="125"/>
+      <c r="L16" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2693,15 +2680,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A59F83D-EB65-4E23-8775-704ADF1A523E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2710,60 +2688,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="133"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="136"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="138">
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="137">
         <v>565</v>
       </c>
-      <c r="E2" s="139"/>
+      <c r="E2" s="138"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="140" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="140" t="s">
+      <c r="A3" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="140" t="s">
+      <c r="C3" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="142" t="s">
+      <c r="D3" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="127" t="s">
+      <c r="E3" s="126" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="127" t="s">
+      <c r="F3" s="126" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="127" t="s">
+      <c r="G3" s="126" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="141"/>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
+      <c r="A4" s="140"/>
+      <c r="B4" s="140"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
@@ -2923,11 +2901,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="129"/>
-      <c r="B12" s="130"/>
-      <c r="C12" s="130"/>
-      <c r="D12" s="130"/>
-      <c r="E12" s="131"/>
+      <c r="A12" s="128"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="130"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>
